--- a/xls/square_12_tri3_8.xlsx
+++ b/xls/square_12_tri3_8.xlsx
@@ -418,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -482,13 +482,13 @@
         <v>384</v>
       </c>
       <c r="I8">
-        <v>3.6716094780163444</v>
+        <v>3.6716095134697357</v>
       </c>
       <c r="J8">
-        <v>0.3742792762086181</v>
+        <v>0.3742793075774059</v>
       </c>
       <c r="K8">
-        <v>1.089896379067571</v>
+        <v>1.0898964261758917</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -517,13 +517,13 @@
         <v>486</v>
       </c>
       <c r="I9">
-        <v>-1.7617870991361684</v>
+        <v>-1.7617868339370732</v>
       </c>
       <c r="J9">
-        <v>-1.6833169406759219</v>
+        <v>-1.6833168105566878</v>
       </c>
       <c r="K9">
-        <v>-1.048855249222111</v>
+        <v>-1.0488552996617395</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -552,13 +552,13 @@
         <v>600</v>
       </c>
       <c r="I10">
-        <v>-1.7546561408378871</v>
+        <v>-1.754655744942633</v>
       </c>
       <c r="J10">
-        <v>-1.7316009206895455</v>
+        <v>-1.7316007071289288</v>
       </c>
       <c r="K10">
-        <v>-1.0852523280632933</v>
+        <v>-1.0852523306182185</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -587,13 +587,13 @@
         <v>726</v>
       </c>
       <c r="I11">
-        <v>-1.7433641080619875</v>
+        <v>-1.7433640717544847</v>
       </c>
       <c r="J11">
-        <v>-1.675356088181136</v>
+        <v>-1.6753560671333043</v>
       </c>
       <c r="K11">
-        <v>-0.8975326282753269</v>
+        <v>-0.8975327366742973</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -622,13 +622,13 @@
         <v>864</v>
       </c>
       <c r="I12">
-        <v>-1.4938164845137845</v>
+        <v>-1.4938165961758259</v>
       </c>
       <c r="J12">
-        <v>-1.1772988954699966</v>
+        <v>-1.1772989239298461</v>
       </c>
       <c r="K12">
-        <v>-0.259365602250488</v>
+        <v>-0.2593656075243037</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -657,13 +657,13 @@
         <v>1014</v>
       </c>
       <c r="I13">
-        <v>-0.5804606989618282</v>
+        <v>-0.5804606895655057</v>
       </c>
       <c r="J13">
-        <v>-0.37623417778802115</v>
+        <v>-0.37623417753686195</v>
       </c>
       <c r="K13">
-        <v>2.8306996364115764</v>
+        <v>2.830699596066749</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -692,13 +692,13 @@
         <v>1176</v>
       </c>
       <c r="I14">
-        <v>-0.0057734797799037256</v>
+        <v>-0.005773479701616095</v>
       </c>
       <c r="J14">
-        <v>-0.004095718054360143</v>
+        <v>-0.004095718006340682</v>
       </c>
       <c r="K14">
-        <v>3.087883624898534</v>
+        <v>3.087883622853968</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -727,13 +727,13 @@
         <v>1350</v>
       </c>
       <c r="I15">
-        <v>-8.699185565749245e-5</v>
+        <v>-8.699185565720309e-5</v>
       </c>
       <c r="J15">
-        <v>-7.432044661957789e-5</v>
+        <v>-7.432044661991547e-5</v>
       </c>
       <c r="K15">
-        <v>2.338192282175459</v>
+        <v>2.338192281764019</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -762,13 +762,573 @@
         <v>1536</v>
       </c>
       <c r="I16">
-        <v>-3.747521709060517e-5</v>
+        <v>-3.747521708930322e-5</v>
       </c>
       <c r="J16">
-        <v>-2.3892585537457463e-5</v>
+        <v>-2.3892585536782395e-5</v>
       </c>
       <c r="K16">
-        <v>1.9139510676703602</v>
+        <v>1.9139510674925042</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17">
+        <v>81</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17">
+        <v>169</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17">
+        <v>324</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17">
+        <v>1734</v>
+      </c>
+      <c r="I17">
+        <v>-6.131599687702701e-6</v>
+      </c>
+      <c r="J17">
+        <v>-5.111303336206363e-6</v>
+      </c>
+      <c r="K17">
+        <v>1.745359339494151</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18">
+        <v>81</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18">
+        <v>169</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18">
+        <v>361</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18">
+        <v>1944</v>
+      </c>
+      <c r="I18">
+        <v>-2.570868157414993e-6</v>
+      </c>
+      <c r="J18">
+        <v>-2.5505074726089625e-6</v>
+      </c>
+      <c r="K18">
+        <v>1.654253989286207</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19">
+        <v>81</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19">
+        <v>169</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19">
+        <v>400</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19">
+        <v>2166</v>
+      </c>
+      <c r="I19">
+        <v>-6.762332397202906e-7</v>
+      </c>
+      <c r="J19">
+        <v>-1.0159947324198974e-6</v>
+      </c>
+      <c r="K19">
+        <v>1.5300846236189318</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20">
+        <v>81</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20">
+        <v>169</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20">
+        <v>441</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20">
+        <v>2400</v>
+      </c>
+      <c r="I20">
+        <v>-3.085763534380945e-7</v>
+      </c>
+      <c r="J20">
+        <v>-3.637351016585515e-7</v>
+      </c>
+      <c r="K20">
+        <v>1.2737021365831345</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21">
+        <v>81</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21">
+        <v>169</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21">
+        <v>484</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21">
+        <v>2646</v>
+      </c>
+      <c r="I21">
+        <v>-1.7984039491221858e-6</v>
+      </c>
+      <c r="J21">
+        <v>-1.3567564266542808e-6</v>
+      </c>
+      <c r="K21">
+        <v>1.4146848664044558</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>81</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22">
+        <v>169</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22">
+        <v>529</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22">
+        <v>2904</v>
+      </c>
+      <c r="I22">
+        <v>-5.092670892640227e-7</v>
+      </c>
+      <c r="J22">
+        <v>-5.106966436341612e-7</v>
+      </c>
+      <c r="K22">
+        <v>1.3106251861256597</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>81</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23">
+        <v>169</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23">
+        <v>576</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23">
+        <v>3174</v>
+      </c>
+      <c r="I23">
+        <v>1.3179623280422323e-7</v>
+      </c>
+      <c r="J23">
+        <v>-1.9793544624321808e-7</v>
+      </c>
+      <c r="K23">
+        <v>1.3386260874781217</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24">
+        <v>81</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24">
+        <v>169</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24">
+        <v>625</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24">
+        <v>3456</v>
+      </c>
+      <c r="I24">
+        <v>-1.2455694900668676e-6</v>
+      </c>
+      <c r="J24">
+        <v>-1.1434198693023091e-6</v>
+      </c>
+      <c r="K24">
+        <v>1.458687943838409</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25">
+        <v>81</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25">
+        <v>169</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25">
+        <v>676</v>
+      </c>
+      <c r="G25" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25">
+        <v>3750</v>
+      </c>
+      <c r="I25">
+        <v>-8.28072768820059e-8</v>
+      </c>
+      <c r="J25">
+        <v>-2.1992820208489454e-7</v>
+      </c>
+      <c r="K25">
+        <v>1.2476054890912578</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26">
+        <v>81</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26">
+        <v>169</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26">
+        <v>729</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26">
+        <v>4056</v>
+      </c>
+      <c r="I26">
+        <v>-3.4146212095297597e-7</v>
+      </c>
+      <c r="J26">
+        <v>-3.2524720392337295e-7</v>
+      </c>
+      <c r="K26">
+        <v>1.2003982901752652</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27">
+        <v>81</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27">
+        <v>169</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27">
+        <v>784</v>
+      </c>
+      <c r="G27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27">
+        <v>4374</v>
+      </c>
+      <c r="I27">
+        <v>-6.002764218022833e-7</v>
+      </c>
+      <c r="J27">
+        <v>-4.81322501090642e-7</v>
+      </c>
+      <c r="K27">
+        <v>1.2228217696455315</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28">
+        <v>81</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28">
+        <v>169</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28">
+        <v>841</v>
+      </c>
+      <c r="G28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28">
+        <v>4704</v>
+      </c>
+      <c r="I28">
+        <v>-2.1912059786717593e-7</v>
+      </c>
+      <c r="J28">
+        <v>-2.0851961226322712e-7</v>
+      </c>
+      <c r="K28">
+        <v>1.1050080752319889</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29">
+        <v>81</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29">
+        <v>169</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29">
+        <v>900</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29">
+        <v>5046</v>
+      </c>
+      <c r="I29">
+        <v>-4.751053667257234e-7</v>
+      </c>
+      <c r="J29">
+        <v>-3.9128067237136846e-7</v>
+      </c>
+      <c r="K29">
+        <v>1.1896993411773829</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30">
+        <v>81</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30">
+        <v>169</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30">
+        <v>961</v>
+      </c>
+      <c r="G30" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30">
+        <v>5400</v>
+      </c>
+      <c r="I30">
+        <v>-2.798555496119124e-7</v>
+      </c>
+      <c r="J30">
+        <v>-2.651294041655062e-7</v>
+      </c>
+      <c r="K30">
+        <v>1.1550735047006826</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31">
+        <v>81</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31">
+        <v>169</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31">
+        <v>1024</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31">
+        <v>5766</v>
+      </c>
+      <c r="I31">
+        <v>-1.7813484919541432e-7</v>
+      </c>
+      <c r="J31">
+        <v>-2.078003765225642e-7</v>
+      </c>
+      <c r="K31">
+        <v>1.1509833817202089</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32">
+        <v>81</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32">
+        <v>169</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32">
+        <v>1089</v>
+      </c>
+      <c r="G32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32">
+        <v>6144</v>
+      </c>
+      <c r="I32">
+        <v>-3.5576537194349074e-7</v>
+      </c>
+      <c r="J32">
+        <v>-3.34446750774395e-7</v>
+      </c>
+      <c r="K32">
+        <v>1.2024952942163458</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_12_tri3_8.xlsx
+++ b/xls/square_12_tri3_8.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="6" spans="1:11">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>81</v>
+      </c>
+      <c r="C6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6">
+        <v>169</v>
+      </c>
+      <c r="E6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6">
+        <v>49</v>
+      </c>
+      <c r="G6" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6">
+        <v>216</v>
+      </c>
+      <c r="I6">
+        <v>24.6437405288434</v>
+      </c>
+      <c r="J6">
+        <v>9.778677188094541</v>
+      </c>
+      <c r="K6">
+        <v>9.60854095643564</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>81</v>
+      </c>
+      <c r="C7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D7">
+        <v>169</v>
+      </c>
+      <c r="E7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7">
+        <v>64</v>
+      </c>
+      <c r="G7" t="s">
+        <v>13</v>
+      </c>
+      <c r="H7">
+        <v>294</v>
+      </c>
+      <c r="I7">
+        <v>5.524577094409589</v>
+      </c>
+      <c r="J7">
+        <v>1.6269954732336986</v>
+      </c>
+      <c r="K7">
+        <v>1.9252567027702674</v>
+      </c>
+    </row>
     <row r="8" spans="1:11">
       <c r="A8" t="s">
         <v>11</v>
